--- a/i_test/test_D6_Table_1/g_output/D6_Table_1_apalu.xlsx
+++ b/i_test/test_D6_Table_1/g_output/D6_Table_1_apalu.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -750,92 +750,92 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>241</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>222</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>171</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>168</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>182</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>163</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>157</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>181</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>171</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -854,92 +854,92 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51 (41 - 65)</t>
+          <t>50 (40 - 58)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5 (40 - 63.25)</t>
+          <t>51 (40 - 62)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52 (41.5 - 60)</t>
+          <t>50.5 (41.25 - 63)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49.5 (42 - 61.25)</t>
+          <t>50.5 (39 - 60)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47 (39 - 56)</t>
+          <t>50 (41 - 60.75)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>53 (42.25 - 62.5)</t>
+          <t>49 (39.75 - 61)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>51 (41 - 63)</t>
+          <t>51 (41 - 60)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>53 (43 - 60)</t>
+          <t>52 (42 - 61.5)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.5 (44.75 - 61)</t>
+          <t>51 (40 - 60.25)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>52 (41.75 - 60.25)</t>
+          <t>50 (40.25 - 61.75)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>49 (37 - 61)</t>
+          <t>50 (39 - 59)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>47 (40 - 59)</t>
+          <t>50 (44 - 60)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>47 (39 - 57)</t>
+          <t>50 (38 - 60)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>49 (39.5 - 57.75)</t>
+          <t>51 (42 - 63)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>48 (43.5 - 56)</t>
+          <t>49 (40 - 61)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>50 (41 - 57)</t>
+          <t>50 (39 - 61)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>52 (41 - 62)</t>
+          <t>49 (39.5 - 59)</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>52 (43.75 - 64.25)</t>
+          <t>51 (41 - 58.75)</t>
         </is>
       </c>
     </row>
@@ -951,92 +951,92 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24 (39,3%)</t>
+          <t>100 (47,6%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>27 (56,2%)</t>
+          <t>119 (49,4%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>36 (64,3%)</t>
+          <t>101 (45,5%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28 (53,8%)</t>
+          <t>93 (45,1%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24 (45,3%)</t>
+          <t>118 (55,1%)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23 (41,1%)</t>
+          <t>110 (50,0%)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>24 (51,1%)</t>
+          <t>74 (47,4%)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>23 (56,1%)</t>
+          <t>89 (52,0%)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20 (45,5%)</t>
+          <t>88 (52,4%)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23 (47,9%)</t>
+          <t>98 (53,8%)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19 (50,0%)</t>
+          <t>92 (50,5%)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20 (48,8%)</t>
+          <t>84 (51,5%)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>28 (52,8%)</t>
+          <t>66 (41,0%)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>22 (50,0%)</t>
+          <t>84 (53,5%)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>22 (46,8%)</t>
+          <t>92 (50,8%)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>22 (56,4%)</t>
+          <t>84 (49,1%)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>21 (51,2%)</t>
+          <t>87 (47,5%)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>24 (54,5%)</t>
+          <t>79 (48,8%)</t>
         </is>
       </c>
     </row>
@@ -1055,92 +1055,92 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>43 (70,5%)</t>
+          <t>133 (63,3%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32 (66,7%)</t>
+          <t>175 (72,6%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35 (62,5%)</t>
+          <t>139 (62,6%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34 (65,4%)</t>
+          <t>143 (69,4%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40 (75,5%)</t>
+          <t>142 (66,4%)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>40 (71,4%)</t>
+          <t>155 (70,5%)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31 (66,0%)</t>
+          <t>105 (67,3%)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28 (68,3%)</t>
+          <t>117 (68,4%)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34 (77,3%)</t>
+          <t>107 (63,7%)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>34 (70,8%)</t>
+          <t>130 (71,4%)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27 (71,1%)</t>
+          <t>127 (69,8%)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>32 (78,0%)</t>
+          <t>113 (69,3%)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>33 (62,3%)</t>
+          <t>112 (69,6%)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>26 (59,1%)</t>
+          <t>119 (75,8%)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>30 (63,8%)</t>
+          <t>124 (68,5%)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>27 (69,2%)</t>
+          <t>118 (69,0%)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>25 (61,0%)</t>
+          <t>120 (65,6%)</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>29 (65,9%)</t>
+          <t>107 (66,0%)</t>
         </is>
       </c>
     </row>
@@ -1152,92 +1152,92 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4 (6,6%)</t>
+          <t>18 (8,6%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4 (8,3%)</t>
+          <t>21 (8,7%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7 (12,5%)</t>
+          <t>22 (9,9%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5 (9,6%)</t>
+          <t>20 (9,7%)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4 (7,5%)</t>
+          <t>21 (9,8%)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1 (1,8%)</t>
+          <t>17 (7,7%)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6 (12,8%)</t>
+          <t>14 (9,0%)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3 (7,3%)</t>
+          <t>13 (7,6%)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3 (6,8%)</t>
+          <t>19 (11,3%)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 (8,3%)</t>
+          <t>10 (5,5%)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7 (18,4%)</t>
+          <t>14 (7,7%)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3 (7,3%)</t>
+          <t>16 (9,8%)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4 (7,5%)</t>
+          <t>16 (9,9%)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4 (9,1%)</t>
+          <t>13 (8,3%)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 (2,1%)</t>
+          <t>5 (2,8%)</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0 (0,0%)</t>
+          <t>16 (9,4%)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>5 (12,2%)</t>
+          <t>16 (8,7%)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1 (2,3%)</t>
+          <t>11 (6,8%)</t>
         </is>
       </c>
     </row>
@@ -1249,92 +1249,92 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23 (37,7%)</t>
+          <t>98 (46,7%)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18 (37,5%)</t>
+          <t>85 (35,3%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18 (32,1%)</t>
+          <t>91 (41,0%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19 (36,5%)</t>
+          <t>104 (50,5%)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21 (39,6%)</t>
+          <t>98 (45,8%)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>26 (46,4%)</t>
+          <t>88 (40,0%)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16 (34,0%)</t>
+          <t>61 (39,1%)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17 (41,5%)</t>
+          <t>71 (41,5%)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18 (40,9%)</t>
+          <t>58 (34,5%)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23 (47,9%)</t>
+          <t>79 (43,4%)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17 (44,7%)</t>
+          <t>73 (40,1%)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>17 (41,5%)</t>
+          <t>57 (35,0%)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>29 (54,7%)</t>
+          <t>68 (42,2%)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>19 (43,2%)</t>
+          <t>66 (42,0%)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>27 (57,4%)</t>
+          <t>71 (39,2%)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>18 (46,2%)</t>
+          <t>61 (35,7%)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>14 (34,1%)</t>
+          <t>70 (38,3%)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>19 (43,2%)</t>
+          <t>64 (39,5%)</t>
         </is>
       </c>
     </row>
@@ -1346,92 +1346,92 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6 (9,8%)</t>
+          <t>20 (9,5%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5 (10,4%)</t>
+          <t>37 (15,4%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11 (19,6%)</t>
+          <t>36 (16,2%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6 (11,5%)</t>
+          <t>24 (11,7%)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7 (13,2%)</t>
+          <t>35 (16,4%)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8 (14,3%)</t>
+          <t>30 (13,6%)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4 (8,5%)</t>
+          <t>29 (18,6%)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8 (19,5%)</t>
+          <t>27 (15,8%)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7 (15,9%)</t>
+          <t>23 (13,7%)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5 (10,4%)</t>
+          <t>34 (18,7%)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4 (10,5%)</t>
+          <t>19 (10,4%)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3 (7,3%)</t>
+          <t>22 (13,5%)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5 (9,4%)</t>
+          <t>25 (15,5%)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4 (9,1%)</t>
+          <t>15 (9,6%)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>9 (19,1%)</t>
+          <t>27 (14,9%)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5 (12,8%)</t>
+          <t>22 (12,9%)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>4 (9,8%)</t>
+          <t>26 (14,2%)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>6 (13,6%)</t>
+          <t>17 (10,5%)</t>
         </is>
       </c>
     </row>
@@ -1443,92 +1443,92 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>52 (85,2%)</t>
+          <t>177 (84,3%)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>38 (79,2%)</t>
+          <t>209 (86,7%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>50 (89,3%)</t>
+          <t>189 (85,1%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44 (84,6%)</t>
+          <t>182 (88,3%)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>47 (88,7%)</t>
+          <t>176 (82,2%)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>43 (76,8%)</t>
+          <t>189 (85,9%)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>40 (85,1%)</t>
+          <t>136 (87,2%)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>39 (95,1%)</t>
+          <t>148 (86,5%)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>38 (86,4%)</t>
+          <t>148 (88,1%)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>38 (79,2%)</t>
+          <t>154 (84,6%)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34 (89,5%)</t>
+          <t>158 (86,8%)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>35 (85,4%)</t>
+          <t>140 (85,9%)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>42 (79,2%)</t>
+          <t>132 (82,0%)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>41 (93,2%)</t>
+          <t>132 (84,1%)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>40 (85,1%)</t>
+          <t>149 (82,3%)</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>35 (89,7%)</t>
+          <t>143 (83,6%)</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>33 (80,5%)</t>
+          <t>152 (83,1%)</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>36 (81,8%)</t>
+          <t>138 (85,2%)</t>
         </is>
       </c>
     </row>
@@ -1540,92 +1540,92 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>52 (85,2%)</t>
+          <t>164 (78,1%)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>40 (83,3%)</t>
+          <t>199 (82,6%)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47 (83,9%)</t>
+          <t>190 (85,6%)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43 (82,7%)</t>
+          <t>183 (88,8%)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45 (84,9%)</t>
+          <t>186 (86,9%)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50 (89,3%)</t>
+          <t>185 (84,1%)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40 (85,1%)</t>
+          <t>131 (84,0%)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>37 (90,2%)</t>
+          <t>144 (84,2%)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38 (86,4%)</t>
+          <t>143 (85,1%)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>41 (85,4%)</t>
+          <t>158 (86,8%)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>27 (71,1%)</t>
+          <t>154 (84,6%)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>39 (95,1%)</t>
+          <t>140 (85,9%)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>45 (84,9%)</t>
+          <t>136 (84,5%)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>37 (84,1%)</t>
+          <t>130 (82,8%)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>43 (91,5%)</t>
+          <t>149 (82,3%)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>33 (84,6%)</t>
+          <t>135 (78,9%)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>36 (87,8%)</t>
+          <t>156 (85,2%)</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>39 (88,6%)</t>
+          <t>137 (84,6%)</t>
         </is>
       </c>
     </row>
@@ -1637,92 +1637,92 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>35 (57,4%)</t>
+          <t>105 (50,0%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>28 (58,3%)</t>
+          <t>126 (52,3%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32 (57,1%)</t>
+          <t>118 (53,2%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24 (46,2%)</t>
+          <t>118 (57,3%)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>27 (50,9%)</t>
+          <t>111 (51,9%)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34 (60,7%)</t>
+          <t>114 (51,8%)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>26 (55,3%)</t>
+          <t>83 (53,2%)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19 (46,3%)</t>
+          <t>103 (60,2%)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15 (34,1%)</t>
+          <t>103 (61,3%)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18 (37,5%)</t>
+          <t>105 (57,7%)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>21 (55,3%)</t>
+          <t>94 (51,6%)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>22 (53,7%)</t>
+          <t>95 (58,3%)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>26 (49,1%)</t>
+          <t>79 (49,1%)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>25 (56,8%)</t>
+          <t>85 (54,1%)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>24 (51,1%)</t>
+          <t>97 (53,6%)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>19 (48,7%)</t>
+          <t>94 (55,0%)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>16 (39,0%)</t>
+          <t>104 (56,8%)</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>25 (56,8%)</t>
+          <t>79 (48,8%)</t>
         </is>
       </c>
     </row>
@@ -1734,92 +1734,92 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16 (26,2%)</t>
+          <t>40 (19,0%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12 (25,0%)</t>
+          <t>45 (18,7%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13 (23,2%)</t>
+          <t>38 (17,1%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12 (23,1%)</t>
+          <t>48 (23,3%)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8 (15,1%)</t>
+          <t>42 (19,6%)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11 (19,6%)</t>
+          <t>37 (16,8%)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8 (17,0%)</t>
+          <t>23 (14,7%)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3 (7,3%)</t>
+          <t>38 (22,2%)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8 (18,2%)</t>
+          <t>27 (16,1%)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>9 (18,8%)</t>
+          <t>38 (20,9%)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5 (13,2%)</t>
+          <t>35 (19,2%)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>8 (19,5%)</t>
+          <t>22 (13,5%)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7 (13,2%)</t>
+          <t>29 (18,0%)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>11 (25,0%)</t>
+          <t>33 (21,0%)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>6 (12,8%)</t>
+          <t>33 (18,2%)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>7 (17,9%)</t>
+          <t>34 (19,9%)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>6 (14,6%)</t>
+          <t>42 (23,0%)</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>6 (13,6%)</t>
+          <t>28 (17,3%)</t>
         </is>
       </c>
     </row>
@@ -1831,92 +1831,92 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5 (8,2%)</t>
+          <t>23 (11,0%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3 (6,2%)</t>
+          <t>21 (8,7%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5 (8,9%)</t>
+          <t>21 (9,5%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3 (5,8%)</t>
+          <t>21 (10,2%)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4 (7,5%)</t>
+          <t>21 (9,8%)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4 (7,1%)</t>
+          <t>23 (10,5%)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3 (6,4%)</t>
+          <t>8 (5,1%)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4 (9,8%)</t>
+          <t>9 (5,3%)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5 (11,4%)</t>
+          <t>14 (8,3%)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>5 (10,4%)</t>
+          <t>16 (8,8%)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6 (15,8%)</t>
+          <t>17 (9,3%)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>4 (9,8%)</t>
+          <t>21 (12,9%)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>4 (7,5%)</t>
+          <t>11 (6,8%)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>6 (13,6%)</t>
+          <t>12 (7,6%)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3 (6,4%)</t>
+          <t>10 (5,5%)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3 (7,7%)</t>
+          <t>14 (8,2%)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>4 (9,8%)</t>
+          <t>9 (4,9%)</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>6 (13,6%)</t>
+          <t>16 (9,9%)</t>
         </is>
       </c>
     </row>
@@ -1928,92 +1928,92 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>56 (91,8%)</t>
+          <t>181 (86,2%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42 (87,5%)</t>
+          <t>216 (89,6%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49 (87,5%)</t>
+          <t>194 (87,4%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44 (84,6%)</t>
+          <t>180 (87,4%)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48 (90,6%)</t>
+          <t>175 (81,8%)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>52 (92,9%)</t>
+          <t>198 (90,0%)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>39 (83,0%)</t>
+          <t>138 (88,5%)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>38 (92,7%)</t>
+          <t>153 (89,5%)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>35 (79,5%)</t>
+          <t>152 (90,5%)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>42 (87,5%)</t>
+          <t>152 (83,5%)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31 (81,6%)</t>
+          <t>164 (90,1%)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>35 (85,4%)</t>
+          <t>147 (90,2%)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>43 (81,1%)</t>
+          <t>147 (91,3%)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>39 (88,6%)</t>
+          <t>145 (92,4%)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>45 (95,7%)</t>
+          <t>158 (87,3%)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>31 (79,5%)</t>
+          <t>150 (87,7%)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>34 (82,9%)</t>
+          <t>160 (87,4%)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>41 (93,2%)</t>
+          <t>136 (84,0%)</t>
         </is>
       </c>
     </row>
@@ -2025,92 +2025,92 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>58 (95,1%)</t>
+          <t>197 (93,8%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>47 (97,9%)</t>
+          <t>231 (95,9%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>55 (98,2%)</t>
+          <t>214 (96,4%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47 (90,4%)</t>
+          <t>196 (95,1%)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>52 (98,1%)</t>
+          <t>200 (93,5%)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>55 (98,2%)</t>
+          <t>203 (92,3%)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>43 (91,5%)</t>
+          <t>145 (92,9%)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>41 (100,0%)</t>
+          <t>159 (93,0%)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>41 (93,2%)</t>
+          <t>161 (95,8%)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>44 (91,7%)</t>
+          <t>165 (90,7%)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>36 (94,7%)</t>
+          <t>172 (94,5%)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>39 (95,1%)</t>
+          <t>151 (92,6%)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>48 (90,6%)</t>
+          <t>152 (94,4%)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>43 (97,7%)</t>
+          <t>141 (89,8%)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>47 (100,0%)</t>
+          <t>164 (90,6%)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>37 (94,9%)</t>
+          <t>162 (94,7%)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>36 (87,8%)</t>
+          <t>173 (94,5%)</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>42 (95,5%)</t>
+          <t>153 (94,4%)</t>
         </is>
       </c>
     </row>
@@ -2122,92 +2122,92 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5 (3 - 7)</t>
+          <t>5 (3 - 6)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3 (2 - 6)</t>
+          <t>4 (3 - 6)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4 (2.75 - 6)</t>
+          <t>4 (3 - 6)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>4 (2 - 7)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>5 (3 - 6)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>5 (2 - 6)</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>4 (2 - 6)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4 (2.75 - 7)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4 (2 - 6)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4 (2 - 6)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>4 (3 - 6)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>4 (3 - 6)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>5 (3 - 6)</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>3 (1.5 - 6)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>4 (2 - 6)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>4 (3 - 6.25)</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4 (2 - 6)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>4 (3 - 7)</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>4 (3 - 6)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>4 (2 - 6.75)</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>4 (3 - 6)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>5 (4 - 7)</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>5 (3 - 6)</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>5 (3 - 6)</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>4 (2 - 6)</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>5 (3 - 6)</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>4 (2.75 - 6)</t>
         </is>
       </c>
     </row>
@@ -2226,92 +2226,92 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>37 (60,7%)</t>
+          <t>117 (55,7%)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>36 (75,0%)</t>
+          <t>153 (63,5%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>39 (69,6%)</t>
+          <t>135 (60,8%)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31 (59,6%)</t>
+          <t>132 (64,1%)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31 (58,5%)</t>
+          <t>136 (63,6%)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>38 (67,9%)</t>
+          <t>131 (59,5%)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>32 (68,1%)</t>
+          <t>90 (57,7%)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20 (48,8%)</t>
+          <t>112 (65,5%)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30 (68,2%)</t>
+          <t>104 (61,9%)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31 (64,6%)</t>
+          <t>109 (59,9%)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25 (65,8%)</t>
+          <t>110 (60,4%)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>26 (63,4%)</t>
+          <t>99 (60,7%)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>29 (54,7%)</t>
+          <t>108 (67,1%)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>25 (56,8%)</t>
+          <t>102 (65,0%)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>25 (53,2%)</t>
+          <t>114 (63,0%)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>26 (66,7%)</t>
+          <t>109 (63,7%)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>24 (58,5%)</t>
+          <t>108 (59,0%)</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>26 (59,1%)</t>
+          <t>99 (61,1%)</t>
         </is>
       </c>
     </row>
@@ -2323,92 +2323,92 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>42 (68,9%)</t>
+          <t>142 (67,6%)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>35 (72,9%)</t>
+          <t>162 (67,2%)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>40 (71,4%)</t>
+          <t>144 (64,9%)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31 (59,6%)</t>
+          <t>125 (60,7%)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>33 (62,3%)</t>
+          <t>139 (65,0%)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>34 (60,7%)</t>
+          <t>151 (68,6%)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>27 (57,4%)</t>
+          <t>97 (62,2%)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>22 (53,7%)</t>
+          <t>109 (63,7%)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28 (63,6%)</t>
+          <t>119 (70,8%)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31 (64,6%)</t>
+          <t>127 (69,8%)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>20 (52,6%)</t>
+          <t>119 (65,4%)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>26 (63,4%)</t>
+          <t>102 (62,6%)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>35 (66,0%)</t>
+          <t>102 (63,4%)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>23 (52,3%)</t>
+          <t>101 (64,3%)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>33 (70,2%)</t>
+          <t>121 (66,9%)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>24 (61,5%)</t>
+          <t>109 (63,7%)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>29 (70,7%)</t>
+          <t>117 (63,9%)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>27 (61,4%)</t>
+          <t>108 (66,7%)</t>
         </is>
       </c>
     </row>
@@ -2420,92 +2420,92 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29 (47,5%)</t>
+          <t>78 (37,1%)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13 (27,1%)</t>
+          <t>82 (34,0%)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24 (42,9%)</t>
+          <t>79 (35,6%)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20 (38,5%)</t>
+          <t>77 (37,4%)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16 (30,2%)</t>
+          <t>79 (36,9%)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24 (42,9%)</t>
+          <t>73 (33,2%)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21 (44,7%)</t>
+          <t>43 (27,6%)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13 (31,7%)</t>
+          <t>53 (31,0%)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16 (36,4%)</t>
+          <t>52 (31,0%)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19 (39,6%)</t>
+          <t>63 (34,6%)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10 (26,3%)</t>
+          <t>58 (31,9%)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16 (39,0%)</t>
+          <t>51 (31,3%)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>20 (37,7%)</t>
+          <t>60 (37,3%)</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>17 (38,6%)</t>
+          <t>55 (35,0%)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>17 (36,2%)</t>
+          <t>55 (30,4%)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>14 (35,9%)</t>
+          <t>61 (35,7%)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10 (24,4%)</t>
+          <t>62 (33,9%)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>17 (38,6%)</t>
+          <t>52 (32,1%)</t>
         </is>
       </c>
     </row>
@@ -2517,92 +2517,92 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20 (32,8%)</t>
+          <t>76 (36,2%)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19 (39,6%)</t>
+          <t>105 (43,6%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19 (33,9%)</t>
+          <t>74 (33,3%)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16 (30,8%)</t>
+          <t>70 (34,0%)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19 (35,8%)</t>
+          <t>82 (38,3%)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17 (30,4%)</t>
+          <t>78 (35,5%)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>16 (34,0%)</t>
+          <t>49 (31,4%)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11 (26,8%)</t>
+          <t>58 (33,9%)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17 (38,6%)</t>
+          <t>58 (34,5%)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21 (43,8%)</t>
+          <t>76 (41,8%)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17 (44,7%)</t>
+          <t>68 (37,4%)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>15 (36,6%)</t>
+          <t>60 (36,8%)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>17 (32,1%)</t>
+          <t>67 (41,6%)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>14 (31,8%)</t>
+          <t>57 (36,3%)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>21 (44,7%)</t>
+          <t>56 (30,9%)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>15 (38,5%)</t>
+          <t>69 (40,4%)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>12 (29,3%)</t>
+          <t>66 (36,1%)</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13 (29,5%)</t>
+          <t>58 (35,8%)</t>
         </is>
       </c>
     </row>
@@ -2614,92 +2614,92 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4 (6,6%)</t>
+          <t>19 (9,0%)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4 (8,3%)</t>
+          <t>15 (6,2%)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0 (0,0%)</t>
+          <t>14 (6,3%)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6 (11,5%)</t>
+          <t>13 (6,3%)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3 (5,7%)</t>
+          <t>13 (6,1%)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3 (5,4%)</t>
+          <t>19 (8,6%)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2 (4,3%)</t>
+          <t>9 (5,8%)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6 (14,6%)</t>
+          <t>12 (7,0%)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2 (4,5%)</t>
+          <t>13 (7,7%)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2 (4,2%)</t>
+          <t>14 (7,7%)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3 (7,9%)</t>
+          <t>6 (3,3%)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2 (4,9%)</t>
+          <t>13 (8,0%)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4 (7,5%)</t>
+          <t>17 (10,6%)</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0 (0,0%)</t>
+          <t>11 (7,0%)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3 (6,4%)</t>
+          <t>16 (8,8%)</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5 (12,8%)</t>
+          <t>12 (7,0%)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>5 (12,2%)</t>
+          <t>18 (9,8%)</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0 (0,0%)</t>
+          <t>16 (9,9%)</t>
         </is>
       </c>
     </row>
@@ -2711,494 +2711,1166 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21 (34,4%)</t>
+          <t>85 (40,5%)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18 (37,5%)</t>
+          <t>86 (35,7%)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19 (33,9%)</t>
+          <t>83 (37,4%)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18 (34,6%)</t>
+          <t>69 (33,5%)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17 (32,1%)</t>
+          <t>79 (36,9%)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22 (39,3%)</t>
+          <t>92 (41,8%)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>27 (57,4%)</t>
+          <t>54 (34,6%)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17 (41,5%)</t>
+          <t>72 (42,1%)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9 (20,5%)</t>
+          <t>61 (36,3%)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17 (35,4%)</t>
+          <t>72 (39,6%)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>20 (52,6%)</t>
+          <t>74 (40,7%)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>14 (34,1%)</t>
+          <t>64 (39,3%)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>22 (41,5%)</t>
+          <t>58 (36,0%)</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>19 (43,2%)</t>
+          <t>60 (38,2%)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>14 (29,8%)</t>
+          <t>63 (34,8%)</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>14 (35,9%)</t>
+          <t>52 (30,4%)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>17 (41,5%)</t>
+          <t>69 (37,7%)</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>17 (38,6%)</t>
+          <t>57 (35,2%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Interruzione trattamento</t>
+          <t>Interruzione trattamento a 12 mesi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>202 (96,2%)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>233 (96,7%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>218 (98,2%)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>198 (96,1%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>204 (95,3%)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>215 (97,7%)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>149 (95,5%)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>166 (97,1%)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>160 (95,2%)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>177 (97,3%)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>178 (97,8%)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>157 (96,3%)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>160 (99,4%)</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>152 (96,8%)</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>177 (97,8%)</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>168 (98,2%)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>181 (98,9%)</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>159 (98,1%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Interruzione trattamento a 24 mesi</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>158 (75,2%)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>169 (70,1%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>157 (70,7%)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>153 (74,3%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>154 (72,0%)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>172 (78,2%)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>117 (75,0%)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>131 (76,6%)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>126 (75,0%)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>136 (74,7%)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>129 (70,9%)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>117 (71,8%)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>119 (73,9%)</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>117 (74,5%)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>138 (76,2%)</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>117 (68,4%)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>130 (71,0%)</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>120 (74,1%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vs apalutamide</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>7 (11,5%)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>6 (12,5%)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>12 (21,4%)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>10 (19,2%)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>8 (15,1%)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>7 (12,5%)</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>5 (10,6%)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6 (14,6%)</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>6 (13,6%)</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>4 (8,3%)</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>4 (10,5%)</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>4 (9,8%)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>5 (9,4%)</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>6 (13,6%)</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>6 (12,8%)</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>5 (12,8%)</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>3 (7,3%)</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>5 (11,4%)</t>
+          <t>Switch</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Vs enzalutamide</t>
+          <t>Vs apalutamide a 12 mesi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6 (9,8%)</t>
+          <t>26 (12,4%)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2 (4,2%)</t>
+          <t>23 (9,5%)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4 (7,1%)</t>
+          <t>28 (12,6%)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8 (15,4%)</t>
+          <t>25 (12,1%)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4 (7,5%)</t>
+          <t>27 (12,6%)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>9 (16,1%)</t>
+          <t>25 (11,4%)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4 (8,5%)</t>
+          <t>23 (14,7%)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3 (7,3%)</t>
+          <t>21 (12,3%)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3 (6,8%)</t>
+          <t>20 (11,9%)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>5 (10,4%)</t>
+          <t>15 (8,2%)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>5 (13,2%)</t>
+          <t>29 (15,9%)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>5 (12,2%)</t>
+          <t>16 (9,8%)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>3 (5,7%)</t>
+          <t>25 (15,5%)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>4 (9,1%)</t>
+          <t>21 (13,4%)</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3 (6,4%)</t>
+          <t>14 (7,7%)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>4 (10,3%)</t>
+          <t>21 (12,3%)</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>4 (9,8%)</t>
+          <t>29 (15,8%)</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>4 (9,1%)</t>
+          <t>21 (13,0%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Vs darolutamide</t>
+          <t>Vs enzalutamide a 12 mesi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>50 (82,0%)</t>
+          <t>15 (7,1%)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>38 (79,2%)</t>
+          <t>24 (10,0%)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>48 (85,7%)</t>
+          <t>22 (9,9%)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>42 (80,8%)</t>
+          <t>16 (7,8%)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>44 (83,0%)</t>
+          <t>17 (7,9%)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>44 (78,6%)</t>
+          <t>15 (6,8%)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>37 (78,7%)</t>
+          <t>17 (10,9%)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30 (73,2%)</t>
+          <t>19 (11,1%)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>38 (86,4%)</t>
+          <t>13 (7,7%)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>39 (81,2%)</t>
+          <t>21 (11,5%)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>35 (92,1%)</t>
+          <t>11 (6,0%)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>36 (87,8%)</t>
+          <t>19 (11,7%)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>43 (81,1%)</t>
+          <t>9 (5,6%)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>33 (75,0%)</t>
+          <t>16 (10,2%)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>37 (78,7%)</t>
+          <t>19 (10,5%)</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>29 (74,4%)</t>
+          <t>17 (9,9%)</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>31 (75,6%)</t>
+          <t>24 (13,1%)</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>39 (88,6%)</t>
+          <t>17 (10,5%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Vs altri farmaci oncologici (L01)</t>
+          <t>Vs darolutamide a 12 mesi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>25 (41,0%)</t>
+          <t>174 (82,9%)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17 (35,4%)</t>
+          <t>193 (80,1%)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23 (41,1%)</t>
+          <t>187 (84,2%)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21 (40,4%)</t>
+          <t>173 (84,0%)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17 (32,1%)</t>
+          <t>168 (78,5%)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15 (26,8%)</t>
+          <t>178 (80,9%)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>16 (34,0%)</t>
+          <t>128 (82,1%)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>18 (43,9%)</t>
+          <t>140 (81,9%)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14 (31,8%)</t>
+          <t>131 (78,0%)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17 (35,4%)</t>
+          <t>150 (82,4%)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>15 (39,5%)</t>
+          <t>148 (81,3%)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15 (36,6%)</t>
+          <t>127 (77,9%)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>23 (43,4%)</t>
+          <t>131 (81,4%)</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>19 (43,2%)</t>
+          <t>126 (80,3%)</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>13 (27,7%)</t>
+          <t>141 (77,9%)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>12 (30,8%)</t>
+          <t>143 (83,6%)</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>12 (29,3%)</t>
+          <t>147 (80,3%)</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>19 (43,2%)</t>
+          <t>125 (77,2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Vs altri farmaci oncologici (L01) a 12 mesi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>65 (31,0%)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>77 (32,0%)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>69 (31,1%)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>56 (27,2%)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>79 (36,9%)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>79 (35,9%)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>47 (30,1%)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>63 (36,8%)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>64 (38,1%)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>52 (28,6%)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>66 (36,3%)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>46 (28,2%)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>59 (36,6%)</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>53 (33,8%)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>73 (40,3%)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>45 (26,3%)</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>72 (39,3%)</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>51 (31,5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Vs apalutamide a 24 mesi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>151 (71,9%)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>175 (72,6%)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>148 (66,7%)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>144 (69,9%)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>155 (72,4%)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>156 (70,9%)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>98 (62,8%)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>116 (67,8%)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>129 (76,8%)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>127 (69,8%)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>132 (72,5%)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>115 (70,6%)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>110 (68,3%)</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>107 (68,2%)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>130 (71,8%)</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>122 (71,3%)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>122 (66,7%)</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>119 (73,5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Vs enzalutamide a 24 mesi</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>30 (14,3%)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>35 (14,5%)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>33 (14,9%)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>28 (13,6%)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>30 (14,0%)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>31 (14,1%)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>30 (19,2%)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30 (17,5%)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>30 (17,9%)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>19 (10,4%)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>35 (19,2%)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>29 (17,8%)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>23 (14,3%)</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>24 (15,3%)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>22 (12,2%)</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>31 (18,1%)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>26 (14,2%)</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>25 (15,4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Vs darolutamide a 24 mesi</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>189 (90,0%)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>218 (90,5%)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>198 (89,2%)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>189 (91,7%)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>200 (93,5%)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>203 (92,3%)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>142 (91,0%)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>152 (88,9%)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>154 (91,7%)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>163 (89,6%)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>167 (91,8%)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>143 (87,7%)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>140 (87,0%)</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>141 (89,8%)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>164 (90,6%)</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>160 (93,6%)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>174 (95,1%)</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>147 (90,7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Vs altri farmaci oncologici (L01) a 24 mesi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>26 (12,4%)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>28 (11,6%)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22 (9,9%)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>24 (11,7%)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>18 (8,4%)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>24 (10,9%)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>17 (10,9%)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>17 (9,9%)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>24 (14,3%)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>23 (12,6%)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>24 (13,2%)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>26 (16,0%)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>18 (11,2%)</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>22 (14,0%)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>11 (6,1%)</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>18 (10,5%)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>24 (13,1%)</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>12 (7,4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ri-iniziatori</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>140 (66,7%)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>150 (62,2%)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>157 (70,7%)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>133 (64,6%)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>122 (57,0%)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>143 (65,0%)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>108 (69,2%)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>114 (66,7%)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>100 (59,5%)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>113 (62,1%)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>118 (64,8%)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>97 (59,5%)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>100 (62,1%)</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>101 (64,3%)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>126 (69,6%)</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>108 (63,2%)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>109 (59,6%)</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>89 (54,9%)</t>
         </is>
       </c>
     </row>
